--- a/docs/Decodifiche/9_dec_tipo_allegato.xlsx
+++ b/docs/Decodifiche/9_dec_tipo_allegato.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="271">
   <si>
     <t>ID</t>
   </si>
@@ -807,6 +807,12 @@
   </si>
   <si>
     <t>Sentenza rettifica sesso</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Provvedimento da Prefettura/Tribunale</t>
   </si>
   <si>
     <t>998</t>
@@ -877,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.37890625" customWidth="true" bestFit="true"/>
@@ -3054,7 +3060,7 @@
         <v>266</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>8</v>
@@ -3078,6 +3084,23 @@
       </c>
       <c r="E129" s="2" t="s">
         <v>267</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
